--- a/EXCEL/Figur3_stillinger.xlsx
+++ b/EXCEL/Figur3_stillinger.xlsx
@@ -160,7 +160,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 11.08.09</t>
+    <t>Kørsel 7.4.2026 11.20.57</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>

--- a/EXCEL/Figur3_stillinger.xlsx
+++ b/EXCEL/Figur3_stillinger.xlsx
@@ -160,7 +160,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 11.20.57</t>
+    <t>Kørsel 7.4.2026 12.44.41</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>

--- a/EXCEL/Figur3_stillinger.xlsx
+++ b/EXCEL/Figur3_stillinger.xlsx
@@ -160,7 +160,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 7.4.2026 12.44.41</t>
+    <t>Kørsel 7.4.2026 12.45.18</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
